--- a/02_Inputs/Data/Charts/Module 5 - Datasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 5 - Datasets for Charts.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28926"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_5FCB38D9107033A2FC33F49D74B161586DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84317FC2-E91B-44B7-9A27-3DE654DD96D5}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Data\Charts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B37CB54-6F32-4C4F-96F2-813DED4CAEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28710" yWindow="-2530" windowWidth="19380" windowHeight="20970" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M5_C1_10" sheetId="1" r:id="rId1"/>
@@ -33,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <si>
     <t>Country</t>
   </si>
@@ -525,13 +530,19 @@
   </si>
   <si>
     <t>Bar48</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Bar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -912,7 +923,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -921,579 +932,579 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC4AFB5D-8F27-41BA-8C11-9BE71AFF251A}">
   <dimension ref="A1:A115"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.75">
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.75">
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75">
+    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75">
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.75">
+    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75">
+    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75">
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15.75">
+    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15.75">
+    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15.75">
+    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15.75">
+    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.75">
+    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="15.75">
+    <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="15.75">
+    <row r="15" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="15.75">
+    <row r="16" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15.75">
+    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15.75">
+    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="15.75">
+    <row r="19" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="15.75">
+    <row r="20" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="15.75">
+    <row r="21" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="15.75">
+    <row r="22" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="15.75">
+    <row r="23" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="15.75">
+    <row r="24" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="15.75">
+    <row r="25" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="15.75">
+    <row r="26" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="15.75">
+    <row r="27" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="15.75">
+    <row r="28" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="15.75">
+    <row r="29" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="15.75">
+    <row r="30" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="15.75">
+    <row r="31" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="15.75">
+    <row r="32" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="15.75">
+    <row r="33" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="15.75">
+    <row r="34" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="15.75">
+    <row r="35" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="15.75">
+    <row r="36" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="15.75">
+    <row r="37" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="15.75">
+    <row r="38" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="15.75">
+    <row r="39" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="15.75">
+    <row r="40" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="15.75">
+    <row r="41" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="15.75">
+    <row r="42" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="15.75">
+    <row r="43" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="15.75">
+    <row r="44" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="15.75">
+    <row r="45" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="15.75">
+    <row r="46" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="15.75">
+    <row r="47" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="15.75">
+    <row r="48" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="15.75">
+    <row r="49" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="15.75">
+    <row r="50" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="15.75">
+    <row r="51" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="15.75">
+    <row r="52" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="15.75">
+    <row r="53" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="15.75">
+    <row r="54" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="15.75">
+    <row r="55" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="15.75">
+    <row r="56" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="15.75">
+    <row r="57" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="15.75">
+    <row r="58" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="15.75">
+    <row r="59" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="15.75">
+    <row r="60" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="15.75">
+    <row r="61" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="15.75">
+    <row r="62" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="15.75">
+    <row r="63" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="15.75">
+    <row r="64" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A64" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" ht="15.75">
+    <row r="65" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="15.75">
+    <row r="66" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A66" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="15.75">
+    <row r="67" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="15.75">
+    <row r="68" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" ht="15.75">
+    <row r="69" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A69" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" ht="15.75">
+    <row r="70" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A70" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" ht="15.75">
+    <row r="71" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A71" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="15.75">
+    <row r="72" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" ht="15.75">
+    <row r="73" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A73" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="15.75">
+    <row r="74" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A74" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" ht="15.75">
+    <row r="75" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A75" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="15.75">
+    <row r="76" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A76" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="15.75">
+    <row r="77" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A77" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="15.75">
+    <row r="78" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A78" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="15.75">
+    <row r="79" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A79" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="15.75">
+    <row r="80" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A80" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" ht="15.75">
+    <row r="81" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A81" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="15.75">
+    <row r="82" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A82" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" ht="15.75">
+    <row r="83" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A83" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="15.75">
+    <row r="84" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A84" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" ht="15.75">
+    <row r="85" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A85" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" ht="15.75">
+    <row r="86" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A86" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" ht="15.75">
+    <row r="87" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A87" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="15.75">
+    <row r="88" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A88" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" ht="15.75">
+    <row r="89" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A89" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" ht="15.75">
+    <row r="90" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A90" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" ht="15.75">
+    <row r="91" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A91" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="15.75">
+    <row r="92" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A92" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" ht="15.75">
+    <row r="93" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A93" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" ht="15.75">
+    <row r="94" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A94" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" ht="15.75">
+    <row r="95" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A95" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" ht="15.75">
+    <row r="96" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A96" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" ht="15.75">
+    <row r="97" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A97" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" ht="15.75">
+    <row r="98" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A98" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" ht="15.75">
+    <row r="99" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A99" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" ht="15.75">
+    <row r="100" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A100" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" ht="15.75">
+    <row r="101" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A101" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" ht="15.75">
+    <row r="102" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A102" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" ht="15.75">
+    <row r="103" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A103" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" ht="15.75">
+    <row r="104" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A104" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" ht="15.75">
+    <row r="105" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A105" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" ht="15.75">
+    <row r="106" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A106" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" ht="15.75">
+    <row r="107" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A107" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" ht="15.75">
+    <row r="108" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A108" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" ht="15.75">
+    <row r="109" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A109" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" ht="15.75">
+    <row r="110" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A110" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" ht="15.75">
+    <row r="111" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A111" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" ht="15.75">
+    <row r="112" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A112" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" ht="15.75">
+    <row r="113" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A113" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" ht="15.75">
+    <row r="114" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A114" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" ht="15.75">
+    <row r="115" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A115" s="1" t="s">
         <v>114</v>
       </c>
@@ -1505,398 +1516,406 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16FA30EE-C30D-4A80-90D2-BCF8619ADFDD}">
-  <dimension ref="A1:B49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B2" s="1">
         <v>8.4030000000000005</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B3" s="1">
         <v>4.1669999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A4" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B4" s="1">
         <v>6.7359999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B5" s="1">
         <v>-10.417</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A6" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="1">
         <v>4.5830000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A7" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="1">
         <v>12.917</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A8" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B8" s="1">
         <v>8.6110000000000007</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A9" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="1">
         <v>4.1669999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A10" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>2.6389999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A11" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="1">
         <v>4.0279999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A12" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B12" s="1">
         <v>-2.153</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75">
-      <c r="A12" s="1" t="s">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A13" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B13" s="1">
         <v>-1.389</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A14" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B14" s="1">
         <v>-1.597</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A15" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B15" s="1">
         <v>1.806</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75">
-      <c r="A15" s="1" t="s">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A16" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B16" s="1">
         <v>2.6389999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A17" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B17" s="1">
         <v>6.319</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A18" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B18" s="1">
         <v>1.25</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A19" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B19" s="1">
         <v>4.444</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A20" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B20" s="1">
         <v>4.0279999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A21" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B21" s="1">
         <v>-8.8190000000000008</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75">
-      <c r="A21" s="1" t="s">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A22" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B22" s="1">
         <v>3.6110000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A23" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B23" s="1">
         <v>1.181</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A24" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B24" s="1">
         <v>6.6669999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A25" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B25" s="1">
         <v>5.3470000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75">
-      <c r="A25" s="1" t="s">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A26" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B26" s="1">
         <v>5.7640000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75">
-      <c r="A26" s="1" t="s">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A27" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B27" s="1">
         <v>4.2359999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75">
-      <c r="A27" s="1" t="s">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A28" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B28" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A29" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B29" s="1">
         <v>5.3470000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75">
-      <c r="A29" s="1" t="s">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A30" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B30" s="1">
         <v>7.8470000000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75">
-      <c r="A30" s="1" t="s">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A31" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B31" s="1">
         <v>3.472</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75">
-      <c r="A31" s="1" t="s">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A32" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B32" s="1">
         <v>4.0279999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75">
-      <c r="A32" s="1" t="s">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A33" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B33" s="1">
         <v>2.9169999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75">
-      <c r="A33" s="1" t="s">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A34" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B34" s="1">
         <v>5.1390000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75">
-      <c r="A34" s="1" t="s">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A35" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="B34" s="1">
-        <v>4.2359999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15.75">
-      <c r="A35" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="B35" s="1">
         <v>4.2359999999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A36" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4.2359999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A37" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B37" s="1">
         <v>2.6389999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75">
-      <c r="A37" s="1" t="s">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A38" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B38" s="1">
         <v>3.819</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A39" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B39" s="1">
         <v>0.41699999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75">
-      <c r="A39" s="1" t="s">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A40" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B40" s="1">
         <v>4.8609999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75">
-      <c r="A40" s="1" t="s">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A41" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B41" s="1">
         <v>0.90300000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75">
-      <c r="A41" s="1" t="s">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A42" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B42" s="1">
         <v>4.2359999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75">
-      <c r="A42" s="1" t="s">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A43" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B43" s="1">
         <v>1.597</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75">
-      <c r="A43" s="1" t="s">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A44" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B44" s="1">
         <v>3.75</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75">
-      <c r="A44" s="1" t="s">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A45" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B45" s="1">
         <v>0.625</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75">
-      <c r="A45" s="1" t="s">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A46" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B46" s="1">
         <v>4.444</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75">
-      <c r="A46" s="1" t="s">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A47" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B47" s="1">
         <v>0.625</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75">
-      <c r="A47" s="1" t="s">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A48" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B48" s="1">
         <v>3.194</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75">
-      <c r="A48" s="1" t="s">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A49" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B49" s="1">
         <v>0.625</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75">
-      <c r="A49" s="1" t="s">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A50" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B50" s="1">
         <v>2.9169999999999998</v>
       </c>
     </row>
@@ -1915,6 +1934,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -2155,25 +2185,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{527AE1AA-7A7D-4A90-ACC9-70ABB77C85C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{527AE1AA-7A7D-4A90-ACC9-70ABB77C85C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87723BFD-F027-418F-A994-887A8E5C7DC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50DB5E95-1533-4238-A73E-10DB663D932B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
+    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50DB5E95-1533-4238-A73E-10DB663D932B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87723BFD-F027-418F-A994-887A8E5C7DC9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
+    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02_Inputs/Data/Charts/Module 5 - Datasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 5 - Datasets for Charts.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28926"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Data\Charts\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B37CB54-6F32-4C4F-96F2-813DED4CAEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_5FCB38D9107033A2FC33F49D74B161586DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84317FC2-E91B-44B7-9A27-3DE654DD96D5}"/>
   <bookViews>
-    <workbookView xWindow="28710" yWindow="-2530" windowWidth="19380" windowHeight="20970" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M5_C1_10" sheetId="1" r:id="rId1"/>
@@ -38,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
   <si>
     <t>Country</t>
   </si>
@@ -530,19 +525,13 @@
   </si>
   <si>
     <t>Bar48</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Bar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -923,7 +912,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -932,579 +921,579 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC4AFB5D-8F27-41BA-8C11-9BE71AFF251A}">
   <dimension ref="A1:A115"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:1" ht="15.75">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:1" ht="15.75">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:1" ht="15.75">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:1" ht="15.75">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:1" ht="15.75">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:1" ht="15.75">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:1" ht="15.75">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:1" ht="15.75">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:1" ht="15.75">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:1" ht="15.75">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:1" ht="15.75">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:1" ht="15.75">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:1" ht="15.75">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:1" ht="15.75">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:1" ht="15.75">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:1" ht="15.75">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:1" ht="15.75">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:1" ht="15.75">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:1" ht="15.75">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:1" ht="15.75">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:1" ht="15.75">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:1" ht="15.75">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:1" ht="15.75">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:1" ht="15.75">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:1" ht="15.75">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:1" ht="15.75">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:1" ht="15.75">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:1" ht="15.75">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:1" ht="15.75">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:1" ht="15.75">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:1" ht="15.75">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:1" ht="15.75">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:1" ht="15.75">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:1" ht="15.75">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:1" ht="15.75">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:1" ht="15.75">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:1" ht="15.75">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:1" ht="15.75">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:1" ht="15.75">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:1" ht="15.75">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:1" ht="15.75">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:1" ht="15.75">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:1" ht="15.75">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:1" ht="15.75">
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:1" ht="15.75">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:1" ht="15.75">
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:1" ht="15.75">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:1" ht="15.75">
       <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:1" ht="15.75">
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:1" ht="15.75">
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:1" ht="15.75">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:1" ht="15.75">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:1" ht="15.75">
       <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:1" ht="15.75">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:1" ht="15.75">
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:1" ht="15.75">
       <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:1" ht="15.75">
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:1" ht="15.75">
       <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:1" ht="15.75">
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:1" ht="15.75">
       <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:1" ht="15.75">
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:1" ht="15.75">
       <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:1" ht="15.75">
       <c r="A64" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:1" ht="15.75">
       <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:1" ht="15.75">
       <c r="A66" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:1" ht="15.75">
       <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:1" ht="15.75">
       <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:1" ht="15.75">
       <c r="A69" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:1" ht="15.75">
       <c r="A70" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:1" ht="15.75">
       <c r="A71" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:1" ht="15.75">
       <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:1" ht="15.75">
       <c r="A73" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:1" ht="15.75">
       <c r="A74" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:1" ht="15.75">
       <c r="A75" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:1" ht="15.75">
       <c r="A76" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:1" ht="15.75">
       <c r="A77" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:1" ht="15.75">
       <c r="A78" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:1" ht="15.75">
       <c r="A79" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:1" ht="15.75">
       <c r="A80" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:1" ht="15.75">
       <c r="A81" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:1" ht="15.75">
       <c r="A82" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:1" ht="15.75">
       <c r="A83" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:1" ht="15.75">
       <c r="A84" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:1" ht="15.75">
       <c r="A85" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:1" ht="15.75">
       <c r="A86" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:1" ht="15.75">
       <c r="A87" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:1" ht="15.75">
       <c r="A88" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:1" ht="15.75">
       <c r="A89" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:1" ht="15.75">
       <c r="A90" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:1" ht="15.75">
       <c r="A91" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:1" ht="15.75">
       <c r="A92" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:1" ht="15.75">
       <c r="A93" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:1" ht="15.75">
       <c r="A94" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:1" ht="15.75">
       <c r="A95" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:1" ht="15.75">
       <c r="A96" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:1" ht="15.75">
       <c r="A97" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:1" ht="15.75">
       <c r="A98" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:1" ht="15.75">
       <c r="A99" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:1" ht="15.75">
       <c r="A100" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:1" ht="15.75">
       <c r="A101" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:1" ht="15.75">
       <c r="A102" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:1" ht="15.75">
       <c r="A103" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:1" ht="15.75">
       <c r="A104" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:1" ht="15.75">
       <c r="A105" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:1" ht="15.75">
       <c r="A106" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:1" ht="15.75">
       <c r="A107" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:1" ht="15.75">
       <c r="A108" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:1" ht="15.75">
       <c r="A109" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:1" ht="15.75">
       <c r="A110" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:1" ht="15.75">
       <c r="A111" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:1" ht="15.75">
       <c r="A112" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:1" ht="15.75">
       <c r="A113" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:1" ht="15.75">
       <c r="A114" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:1" ht="15.75">
       <c r="A115" s="1" t="s">
         <v>114</v>
       </c>
@@ -1516,406 +1505,398 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16FA30EE-C30D-4A80-90D2-BCF8619ADFDD}">
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="15.75">
+      <c r="A1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="1">
+        <v>8.4030000000000005</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75">
       <c r="A2" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1">
-        <v>8.4030000000000005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+        <v>4.1669999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B3" s="1">
+        <v>6.7359999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75">
+      <c r="A4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="1">
+        <v>-10.417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75">
+      <c r="A5" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4.5830000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75">
+      <c r="A6" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="1">
+        <v>12.917</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75">
+      <c r="A7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="1">
+        <v>8.6110000000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75">
+      <c r="A8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="1">
         <v>4.1669999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="1">
-        <v>6.7359999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A5" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="1">
-        <v>-10.417</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A6" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="1">
-        <v>4.5830000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A7" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="1">
-        <v>12.917</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A8" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="1">
-        <v>8.6110000000000007</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" ht="15.75">
       <c r="A9" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B9" s="1">
-        <v>4.1669999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+        <v>2.6389999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.75">
       <c r="A10" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B10" s="1">
+        <v>4.0279999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75">
+      <c r="A11" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="1">
+        <v>-2.153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75">
+      <c r="A12" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-1.389</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75">
+      <c r="A13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-1.597</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75">
+      <c r="A14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1.806</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.75">
+      <c r="A15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="1">
         <v>2.6389999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A11" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="16" spans="1:2" ht="15.75">
+      <c r="A16" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="1">
+        <v>6.319</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75">
+      <c r="A17" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75">
+      <c r="A18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="1">
+        <v>4.444</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75">
+      <c r="A19" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="1">
         <v>4.0279999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A12" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="1">
-        <v>-2.153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A13" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="1">
-        <v>-1.389</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A14" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="1">
-        <v>-1.597</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A15" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1.806</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A16" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B16" s="1">
-        <v>2.6389999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A17" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B17" s="1">
-        <v>6.319</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A18" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B18" s="1">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A19" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="1">
-        <v>4.444</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" ht="15.75">
       <c r="A20" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="1">
+        <v>-8.8190000000000008</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75">
+      <c r="A21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3.6110000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75">
+      <c r="A22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1.181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75">
+      <c r="A23" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="1">
+        <v>6.6669999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75">
+      <c r="A24" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="1">
+        <v>5.3470000000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75">
+      <c r="A25" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" s="1">
+        <v>5.7640000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75">
+      <c r="A26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="1">
+        <v>4.2359999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75">
+      <c r="A27" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75">
+      <c r="A28" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" s="1">
+        <v>5.3470000000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75">
+      <c r="A29" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="1">
+        <v>7.8470000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.75">
+      <c r="A30" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="1">
+        <v>3.472</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75">
+      <c r="A31" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31" s="1">
         <v>4.0279999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A21" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B21" s="1">
-        <v>-8.8190000000000008</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A22" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="1">
-        <v>3.6110000000000002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A23" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1.181</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A24" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B24" s="1">
-        <v>6.6669999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A25" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B25" s="1">
-        <v>5.3470000000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A26" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B26" s="1">
-        <v>5.7640000000000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A27" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B27" s="1">
+    <row r="32" spans="1:2" ht="15.75">
+      <c r="A32" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" s="1">
+        <v>2.9169999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75">
+      <c r="A33" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="1">
+        <v>5.1390000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75">
+      <c r="A34" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" s="1">
         <v>4.2359999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A28" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B28" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A29" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B29" s="1">
-        <v>5.3470000000000004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A30" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B30" s="1">
-        <v>7.8470000000000004</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A31" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B31" s="1">
-        <v>3.472</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A32" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B32" s="1">
-        <v>4.0279999999999996</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A33" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2.9169999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A34" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B34" s="1">
-        <v>5.1390000000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" ht="15.75">
       <c r="A35" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B35" s="1">
         <v>4.2359999999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" ht="15.75">
       <c r="A36" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B36" s="1">
+        <v>2.6389999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75">
+      <c r="A37" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3.819</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75">
+      <c r="A38" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.41699999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75">
+      <c r="A39" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B39" s="1">
+        <v>4.8609999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75">
+      <c r="A40" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0.90300000000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75">
+      <c r="A41" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B41" s="1">
         <v>4.2359999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A37" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B37" s="1">
-        <v>2.6389999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A38" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B38" s="1">
-        <v>3.819</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A39" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0.41699999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A40" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B40" s="1">
-        <v>4.8609999999999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A41" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" s="1">
-        <v>0.90300000000000002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:2" ht="15.75">
       <c r="A42" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="1">
-        <v>4.2359999999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+        <v>1.597</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75">
       <c r="A43" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="1">
-        <v>1.597</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75">
       <c r="A44" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="1">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75">
       <c r="A45" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B45" s="1">
+        <v>4.444</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75">
+      <c r="A46" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B46" s="1">
         <v>0.625</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A46" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B46" s="1">
-        <v>4.444</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:2" ht="15.75">
       <c r="A47" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B47" s="1">
+        <v>3.194</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75">
+      <c r="A48" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B48" s="1">
         <v>0.625</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A48" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B48" s="1">
-        <v>3.194</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:2" ht="15.75">
       <c r="A49" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B49" s="1">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A50" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B50" s="1">
         <v>2.9169999999999998</v>
       </c>
     </row>
@@ -1934,17 +1915,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -2185,40 +2155,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{527AE1AA-7A7D-4A90-ACC9-70ABB77C85C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{527AE1AA-7A7D-4A90-ACC9-70ABB77C85C4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50DB5E95-1533-4238-A73E-10DB663D932B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87723BFD-F027-418F-A994-887A8E5C7DC9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87723BFD-F027-418F-A994-887A8E5C7DC9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50DB5E95-1533-4238-A73E-10DB663D932B}"/>
 </file>
--- a/02_Inputs/Data/Charts/Module 5 - Datasets for Charts.xlsx
+++ b/02_Inputs/Data/Charts/Module 5 - Datasets for Charts.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28926"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29012"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_5FCB38D9107033A2FC33F49D74B161586DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84317FC2-E91B-44B7-9A27-3DE654DD96D5}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_5FCB38D9107033A2FC33F49D74B161586DDE5F8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6739021D-5928-4AD0-B063-7641133971A3}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M5_C1_10" sheetId="1" r:id="rId1"/>
@@ -911,6 +911,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
@@ -920,6 +923,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC4AFB5D-8F27-41BA-8C11-9BE71AFF251A}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:A115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1505,6 +1511,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16FA30EE-C30D-4A80-90D2-BCF8619ADFDD}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1906,12 +1915,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2156,18 +2167,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{527AE1AA-7A7D-4A90-ACC9-70ABB77C85C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50DB5E95-1533-4238-A73E-10DB663D932B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2175,5 +2184,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50DB5E95-1533-4238-A73E-10DB663D932B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{527AE1AA-7A7D-4A90-ACC9-70ABB77C85C4}"/>
 </file>